--- a/data/trans_orig/P64D1_R-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P64D1_R-Habitat-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>83889</t>
+          <t>95691</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>69391</t>
+          <t>78335</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>101019</t>
+          <t>115096</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>25,19%</t>
+          <t>26,08%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>20,83%</t>
+          <t>21,35%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>30,33%</t>
+          <t>31,37%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>98537</t>
+          <t>104007</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>85713</t>
+          <t>90630</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>111911</t>
+          <t>118904</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>38,18%</t>
+          <t>37,28%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>33,21%</t>
+          <t>32,48%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>43,37%</t>
+          <t>42,62%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>182427</t>
+          <t>199697</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>161718</t>
+          <t>177363</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>203874</t>
+          <t>221656</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>30,86%</t>
+          <t>30,92%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>27,36%</t>
+          <t>27,46%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>34,49%</t>
+          <t>34,32%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>249186</t>
+          <t>271156</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>232056</t>
+          <t>251751</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>263684</t>
+          <t>288512</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>74,81%</t>
+          <t>73,92%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>69,67%</t>
+          <t>68,63%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>79,17%</t>
+          <t>78,65%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>159528</t>
+          <t>175002</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>146154</t>
+          <t>160105</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>172352</t>
+          <t>188379</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>61,82%</t>
+          <t>62,72%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>56,63%</t>
+          <t>57,38%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>66,79%</t>
+          <t>67,52%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>408712</t>
+          <t>446159</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>387265</t>
+          <t>424200</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>429421</t>
+          <t>468493</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>69,14%</t>
+          <t>69,08%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>65,51%</t>
+          <t>65,68%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>72,64%</t>
+          <t>72,54%</t>
         </is>
       </c>
     </row>
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>333075</t>
+          <t>366847</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>333075</t>
+          <t>366847</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>333075</t>
+          <t>366847</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>258065</t>
+          <t>279009</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>258065</t>
+          <t>279009</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>258065</t>
+          <t>279009</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>591139</t>
+          <t>645856</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>591139</t>
+          <t>645856</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>591139</t>
+          <t>645856</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,32 +1068,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>132048</t>
+          <t>160825</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>57438</t>
+          <t>135859</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>201394</t>
+          <t>184186</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>16,39%</t>
+          <t>25,61%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>21,63%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>29,33%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1103,32 +1103,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>166723</t>
+          <t>187914</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>150105</t>
+          <t>168197</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>184092</t>
+          <t>207309</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>41,59%</t>
+          <t>42,03%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>37,44%</t>
+          <t>37,62%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>45,92%</t>
+          <t>46,37%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>298771</t>
+          <t>348739</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>159756</t>
+          <t>317240</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>386526</t>
+          <t>380541</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>24,77%</t>
+          <t>32,44%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>29,51%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>32,04%</t>
+          <t>35,4%</t>
         </is>
       </c>
     </row>
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>673436</t>
+          <t>467216</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>604090</t>
+          <t>443855</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>748046</t>
+          <t>492182</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>83,61%</t>
+          <t>74,39%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>75,0%</t>
+          <t>70,67%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>92,87%</t>
+          <t>78,37%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>234158</t>
+          <t>259148</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>216789</t>
+          <t>239753</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>250776</t>
+          <t>278865</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>58,41%</t>
+          <t>57,97%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>54,08%</t>
+          <t>53,63%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>62,56%</t>
+          <t>62,38%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>907593</t>
+          <t>726364</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>819838</t>
+          <t>694562</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1046608</t>
+          <t>757863</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>75,23%</t>
+          <t>67,56%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>67,96%</t>
+          <t>64,6%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>86,76%</t>
+          <t>70,49%</t>
         </is>
       </c>
     </row>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>805484</t>
+          <t>628041</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>805484</t>
+          <t>628041</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>805484</t>
+          <t>628041</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>400881</t>
+          <t>447062</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>400881</t>
+          <t>447062</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>400881</t>
+          <t>447062</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1206364</t>
+          <t>1075103</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1206364</t>
+          <t>1075103</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1206364</t>
+          <t>1075103</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,32 +1411,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>60527</t>
+          <t>73583</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>46932</t>
+          <t>55962</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>80131</t>
+          <t>94705</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>17,0%</t>
+          <t>17,62%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>13,18%</t>
+          <t>13,4%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>22,51%</t>
+          <t>22,68%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1446,32 +1446,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>75044</t>
+          <t>95770</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>51847</t>
+          <t>81874</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>91093</t>
+          <t>112108</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>23,28%</t>
+          <t>28,37%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16,08%</t>
+          <t>24,25%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>28,26%</t>
+          <t>33,21%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>135571</t>
+          <t>169353</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>110887</t>
+          <t>148312</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>160485</t>
+          <t>193859</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>19,98%</t>
+          <t>22,43%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>16,34%</t>
+          <t>19,64%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>23,66%</t>
+          <t>25,67%</t>
         </is>
       </c>
     </row>
@@ -1524,32 +1524,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>295509</t>
+          <t>343987</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>275905</t>
+          <t>322865</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>309104</t>
+          <t>361608</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>83,0%</t>
+          <t>82,38%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>77,49%</t>
+          <t>77,32%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>86,82%</t>
+          <t>86,6%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1559,32 +1559,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>247349</t>
+          <t>241795</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>231300</t>
+          <t>225457</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>270546</t>
+          <t>255691</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>76,72%</t>
+          <t>71,63%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>71,74%</t>
+          <t>66,79%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>83,92%</t>
+          <t>75,75%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>542858</t>
+          <t>585782</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>517944</t>
+          <t>561276</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>567542</t>
+          <t>606823</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>80,02%</t>
+          <t>77,57%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>76,34%</t>
+          <t>74,33%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>83,66%</t>
+          <t>80,36%</t>
         </is>
       </c>
     </row>
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>356036</t>
+          <t>417570</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>356036</t>
+          <t>417570</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>356036</t>
+          <t>417570</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>322393</t>
+          <t>337565</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>322393</t>
+          <t>337565</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>322393</t>
+          <t>337565</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>678429</t>
+          <t>755135</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>678429</t>
+          <t>755135</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>678429</t>
+          <t>755135</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,32 +1754,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>131520</t>
+          <t>146980</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>112082</t>
+          <t>127783</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>153133</t>
+          <t>173535</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>27,92%</t>
+          <t>28,44%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>23,79%</t>
+          <t>24,73%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>32,51%</t>
+          <t>33,58%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,32 +1789,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>235952</t>
+          <t>182876</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>186408</t>
+          <t>163572</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>332674</t>
+          <t>200315</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>49,2%</t>
+          <t>40,85%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>38,87%</t>
+          <t>36,54%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>69,37%</t>
+          <t>44,75%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>367473</t>
+          <t>329856</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>311226</t>
+          <t>304005</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>501086</t>
+          <t>357622</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>38,65%</t>
+          <t>34,2%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>32,74%</t>
+          <t>31,52%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>52,71%</t>
+          <t>37,08%</t>
         </is>
       </c>
     </row>
@@ -1867,32 +1867,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>339571</t>
+          <t>369737</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>317958</t>
+          <t>343182</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>359009</t>
+          <t>388934</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>72,08%</t>
+          <t>71,56%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>67,49%</t>
+          <t>66,42%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>76,21%</t>
+          <t>75,27%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,32 +1902,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>243645</t>
+          <t>264786</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>146923</t>
+          <t>247347</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>293189</t>
+          <t>284090</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>50,8%</t>
+          <t>59,15%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>30,63%</t>
+          <t>55,25%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>61,13%</t>
+          <t>63,46%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>583215</t>
+          <t>634523</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>449602</t>
+          <t>606757</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>639462</t>
+          <t>660374</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>61,35%</t>
+          <t>65,8%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>47,29%</t>
+          <t>62,92%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>67,26%</t>
+          <t>68,48%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>471091</t>
+          <t>516717</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>471091</t>
+          <t>516717</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>471091</t>
+          <t>516717</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>479597</t>
+          <t>447662</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>479597</t>
+          <t>447662</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>479597</t>
+          <t>447662</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>950688</t>
+          <t>964379</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>950688</t>
+          <t>964379</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>950688</t>
+          <t>964379</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2097,32 +2097,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>407985</t>
+          <t>477078</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>274125</t>
+          <t>435206</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>478461</t>
+          <t>519577</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>20,76%</t>
+          <t>24,73%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>13,95%</t>
+          <t>22,56%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>24,34%</t>
+          <t>26,93%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,32 +2132,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>576256</t>
+          <t>570567</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>516941</t>
+          <t>537411</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>709865</t>
+          <t>603879</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>39,44%</t>
+          <t>37,75%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>35,38%</t>
+          <t>35,56%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>48,59%</t>
+          <t>39,96%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>984242</t>
+          <t>1047645</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>808557</t>
+          <t>992323</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1142099</t>
+          <t>1098725</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>28,72%</t>
+          <t>30,45%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>23,6%</t>
+          <t>28,84%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>33,33%</t>
+          <t>31,94%</t>
         </is>
       </c>
     </row>
@@ -2210,32 +2210,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1557701</t>
+          <t>1452097</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1487225</t>
+          <t>1409598</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1691561</t>
+          <t>1493969</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>79,24%</t>
+          <t>75,27%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>75,66%</t>
+          <t>73,07%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>86,05%</t>
+          <t>77,44%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,32 +2245,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>884679</t>
+          <t>940731</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>751070</t>
+          <t>907419</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>943994</t>
+          <t>973887</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>60,56%</t>
+          <t>62,25%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>51,41%</t>
+          <t>60,04%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>64,62%</t>
+          <t>64,44%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>2442380</t>
+          <t>2392828</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2284523</t>
+          <t>2341748</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>2618065</t>
+          <t>2448150</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>71,28%</t>
+          <t>69,55%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>66,67%</t>
+          <t>68,06%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>76,4%</t>
+          <t>71,16%</t>
         </is>
       </c>
     </row>
@@ -2323,17 +2323,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1965686</t>
+          <t>1929175</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1965686</t>
+          <t>1929175</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1965686</t>
+          <t>1929175</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2358,17 +2358,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1460935</t>
+          <t>1511298</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1460935</t>
+          <t>1511298</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>1460935</t>
+          <t>1511298</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>3426622</t>
+          <t>3440473</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>3426622</t>
+          <t>3440473</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>3426622</t>
+          <t>3440473</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
